--- a/data/nzd0177/nzd0177.xlsx
+++ b/data/nzd0177/nzd0177.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J368"/>
+  <dimension ref="A1:J372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13684,6 +13684,150 @@
         <v>370.83</v>
       </c>
       <c r="J368" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>367.61</v>
+      </c>
+      <c r="C369" t="n">
+        <v>365.1</v>
+      </c>
+      <c r="D369" t="n">
+        <v>366.63</v>
+      </c>
+      <c r="E369" t="n">
+        <v>370.38</v>
+      </c>
+      <c r="F369" t="n">
+        <v>371.47</v>
+      </c>
+      <c r="G369" t="n">
+        <v>373.45</v>
+      </c>
+      <c r="H369" t="n">
+        <v>366</v>
+      </c>
+      <c r="I369" t="n">
+        <v>370.16</v>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>367.72</v>
+      </c>
+      <c r="C370" t="n">
+        <v>366.23</v>
+      </c>
+      <c r="D370" t="n">
+        <v>367.33</v>
+      </c>
+      <c r="E370" t="n">
+        <v>371.64</v>
+      </c>
+      <c r="F370" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="G370" t="n">
+        <v>374.87</v>
+      </c>
+      <c r="H370" t="n">
+        <v>368.06</v>
+      </c>
+      <c r="I370" t="n">
+        <v>372.76</v>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>368.37</v>
+      </c>
+      <c r="C371" t="n">
+        <v>366.35</v>
+      </c>
+      <c r="D371" t="n">
+        <v>367.82</v>
+      </c>
+      <c r="E371" t="n">
+        <v>372.55</v>
+      </c>
+      <c r="F371" t="n">
+        <v>372.55</v>
+      </c>
+      <c r="G371" t="n">
+        <v>374.67</v>
+      </c>
+      <c r="H371" t="n">
+        <v>367.26</v>
+      </c>
+      <c r="I371" t="n">
+        <v>371.57</v>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>369.21</v>
+      </c>
+      <c r="C372" t="n">
+        <v>366.28</v>
+      </c>
+      <c r="D372" t="n">
+        <v>367.8</v>
+      </c>
+      <c r="E372" t="n">
+        <v>372.98</v>
+      </c>
+      <c r="F372" t="n">
+        <v>373.06</v>
+      </c>
+      <c r="G372" t="n">
+        <v>374.99</v>
+      </c>
+      <c r="H372" t="n">
+        <v>367.47</v>
+      </c>
+      <c r="I372" t="n">
+        <v>371.52</v>
+      </c>
+      <c r="J372" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13700,7 +13844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B378"/>
+  <dimension ref="A1:B382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17483,6 +17627,46 @@
       </c>
       <c r="B378" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>-0.32</v>
       </c>
     </row>
   </sheetData>
@@ -17651,28 +17835,28 @@
         <v>0.1672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3229230827298532</v>
+        <v>0.3150783242444298</v>
       </c>
       <c r="J2" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K2" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1765745661118064</v>
+        <v>0.1722751483966736</v>
       </c>
       <c r="M2" t="n">
-        <v>4.158812921096131</v>
+        <v>4.143185542662979</v>
       </c>
       <c r="N2" t="n">
-        <v>27.46292799198241</v>
+        <v>27.3122998224746</v>
       </c>
       <c r="O2" t="n">
-        <v>5.240508371521069</v>
+        <v>5.226117088477314</v>
       </c>
       <c r="P2" t="n">
-        <v>363.1924268714994</v>
+        <v>363.2757243135745</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17733,28 +17917,28 @@
         <v>0.1707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2600205030956219</v>
+        <v>0.2605000183591167</v>
       </c>
       <c r="J3" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K3" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1892091231354472</v>
+        <v>0.1935651748962025</v>
       </c>
       <c r="M3" t="n">
-        <v>3.150424349944955</v>
+        <v>3.122699740060215</v>
       </c>
       <c r="N3" t="n">
-        <v>16.36192877738137</v>
+        <v>16.18882847495067</v>
       </c>
       <c r="O3" t="n">
-        <v>4.044988105962905</v>
+        <v>4.023534326304508</v>
       </c>
       <c r="P3" t="n">
-        <v>358.7435866668688</v>
+        <v>358.7384848564854</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17815,28 +17999,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2224796891085909</v>
+        <v>0.2233150751208825</v>
       </c>
       <c r="J4" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K4" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1505254926761838</v>
+        <v>0.1546505739812393</v>
       </c>
       <c r="M4" t="n">
-        <v>3.07503609315953</v>
+        <v>3.047964137677276</v>
       </c>
       <c r="N4" t="n">
-        <v>15.77515227018201</v>
+        <v>15.60912880495786</v>
       </c>
       <c r="O4" t="n">
-        <v>3.971794590633056</v>
+        <v>3.950839000131221</v>
       </c>
       <c r="P4" t="n">
-        <v>360.9951120603711</v>
+        <v>360.9862299276838</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -17897,28 +18081,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1261804650324932</v>
+        <v>0.1288651145494793</v>
       </c>
       <c r="J5" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K5" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07076600143349854</v>
+        <v>0.0751239513922195</v>
       </c>
       <c r="M5" t="n">
-        <v>2.760386616320351</v>
+        <v>2.744060327098376</v>
       </c>
       <c r="N5" t="n">
-        <v>11.80693604487169</v>
+        <v>11.70667854935197</v>
       </c>
       <c r="O5" t="n">
-        <v>3.436122239512396</v>
+        <v>3.421502381900672</v>
       </c>
       <c r="P5" t="n">
-        <v>367.2234843339543</v>
+        <v>367.1949507022223</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -17979,28 +18163,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04272293098979737</v>
+        <v>0.05050007862373473</v>
       </c>
       <c r="J6" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K6" t="n">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004499134896511769</v>
+        <v>0.006391469804014061</v>
       </c>
       <c r="M6" t="n">
-        <v>3.635514791128943</v>
+        <v>3.631933495654563</v>
       </c>
       <c r="N6" t="n">
-        <v>22.6025082960923</v>
+        <v>22.49876974892302</v>
       </c>
       <c r="O6" t="n">
-        <v>4.754209534306654</v>
+        <v>4.743286808629962</v>
       </c>
       <c r="P6" t="n">
-        <v>367.6808485468923</v>
+        <v>367.5977084977242</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -18061,28 +18245,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1036784371551065</v>
+        <v>-0.09036548803149649</v>
       </c>
       <c r="J7" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K7" t="n">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02050062762235449</v>
+        <v>0.01581556566404718</v>
       </c>
       <c r="M7" t="n">
-        <v>4.423087259341401</v>
+        <v>4.438358879922647</v>
       </c>
       <c r="N7" t="n">
-        <v>28.74324654150772</v>
+        <v>28.83746311430171</v>
       </c>
       <c r="O7" t="n">
-        <v>5.361272847142525</v>
+        <v>5.370052431243265</v>
       </c>
       <c r="P7" t="n">
-        <v>371.0932916173415</v>
+        <v>370.9509810111816</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -18143,28 +18327,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1582351760999512</v>
+        <v>-0.1473890492585558</v>
       </c>
       <c r="J8" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K8" t="n">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04861164069580082</v>
+        <v>0.04305440587939435</v>
       </c>
       <c r="M8" t="n">
-        <v>4.319227039434643</v>
+        <v>4.328517300259874</v>
       </c>
       <c r="N8" t="n">
-        <v>27.42493168791926</v>
+        <v>27.4006063995948</v>
       </c>
       <c r="O8" t="n">
-        <v>5.236881866905082</v>
+        <v>5.234558854344347</v>
       </c>
       <c r="P8" t="n">
-        <v>366.421405167506</v>
+        <v>366.3054639484853</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -18225,28 +18409,28 @@
         <v>0.1442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1287558758532343</v>
+        <v>-0.1194924129923515</v>
       </c>
       <c r="J9" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K9" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03732350785751726</v>
+        <v>0.03282032151823089</v>
       </c>
       <c r="M9" t="n">
-        <v>3.929249796998674</v>
+        <v>3.930492227341552</v>
       </c>
       <c r="N9" t="n">
-        <v>24.14818846095735</v>
+        <v>24.09366399703944</v>
       </c>
       <c r="O9" t="n">
-        <v>4.914080632321508</v>
+        <v>4.908529718463507</v>
       </c>
       <c r="P9" t="n">
-        <v>370.6311884128236</v>
+        <v>370.5328027290107</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -18288,7 +18472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J368"/>
+  <dimension ref="A1:J372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37415,6 +37599,214 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>-36.827166726057825,175.71489235952515</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>-36.827814620090926,175.71528729248325</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>-36.828459863980136,175.71568410671563</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>-36.82908241140605,175.71611442497422</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>-36.829667476461424,175.71661397631624</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>-36.830209896803474,175.71716657896</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>-36.83070486295051,175.71779801229727</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>-36.83107864686586,175.71856186332883</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>-36.827166248438665,175.71489343949943</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>-36.82780992351224,175.71529852652517</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>-36.82845702802909,175.71569111266237</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>-36.829076571036175,175.7161265316913</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>-36.829660631700264,175.7166253796364</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>-36.830200777256216,175.71717773731856</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>-36.830689788225214,175.7178114743044</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>-36.831059093525475,175.71857790170233</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>-36.82716342614343,175.71489982116526</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>-36.82780942476046,175.7152997195207</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>-36.828455042863155,175.71569601682478</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>-36.82907235299053,175.7161352754302</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>-36.82966165571971,175.71662367362802</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>-36.83020206169955,175.71717616571894</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>-36.83069564248763,175.71780624634107</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>-36.8310680429392,175.71857056106316</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>-36.8271597788691,175.71490806824042</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>-36.827809715699004,175.71529902360663</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>-36.828455123890336,175.71569581665491</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>-36.829070359847876,175.71613940708667</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>-36.82965890703587,175.7166282529136</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>-36.83020000659021,175.71717868027832</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>-36.83069410574376,175.71780761868152</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>-36.831068418964975,175.7185702526329</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0177/nzd0177.xlsx
+++ b/data/nzd0177/nzd0177.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J372"/>
+  <dimension ref="A1:J373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13830,6 +13830,42 @@
       <c r="J372" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>369.85</v>
+      </c>
+      <c r="C373" t="n">
+        <v>365.95</v>
+      </c>
+      <c r="D373" t="n">
+        <v>368.17</v>
+      </c>
+      <c r="E373" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="F373" t="n">
+        <v>374.29</v>
+      </c>
+      <c r="G373" t="n">
+        <v>376.75</v>
+      </c>
+      <c r="H373" t="n">
+        <v>369.14</v>
+      </c>
+      <c r="I373" t="n">
+        <v>371.53</v>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13844,7 +13880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B382"/>
+  <dimension ref="A1:B383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17667,6 +17703,16 @@
       </c>
       <c r="B382" t="n">
         <v>-0.32</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -17835,28 +17881,28 @@
         <v>0.1672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3150783242444298</v>
+        <v>0.3140450236980741</v>
       </c>
       <c r="J2" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K2" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1722751483966736</v>
+        <v>0.1721480991192771</v>
       </c>
       <c r="M2" t="n">
-        <v>4.143185542662979</v>
+        <v>4.135909311755986</v>
       </c>
       <c r="N2" t="n">
-        <v>27.3122998224746</v>
+        <v>27.24898909079061</v>
       </c>
       <c r="O2" t="n">
-        <v>5.226117088477314</v>
+        <v>5.220056426015969</v>
       </c>
       <c r="P2" t="n">
-        <v>363.2757243135745</v>
+        <v>363.2867231718207</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17917,28 +17963,28 @@
         <v>0.1707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2605000183591167</v>
+        <v>0.2605866675876077</v>
       </c>
       <c r="J3" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K3" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1935651748962025</v>
+        <v>0.1946148018563556</v>
       </c>
       <c r="M3" t="n">
-        <v>3.122699740060215</v>
+        <v>3.114795169649379</v>
       </c>
       <c r="N3" t="n">
-        <v>16.18882847495067</v>
+        <v>16.14538120788583</v>
       </c>
       <c r="O3" t="n">
-        <v>4.023534326304508</v>
+        <v>4.018131556816654</v>
       </c>
       <c r="P3" t="n">
-        <v>358.7384848564854</v>
+        <v>358.7375625279483</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17999,28 +18045,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2233150751208825</v>
+        <v>0.2239228301669287</v>
       </c>
       <c r="J4" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K4" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1546505739812393</v>
+        <v>0.156128449972663</v>
       </c>
       <c r="M4" t="n">
-        <v>3.047964137677276</v>
+        <v>3.042742613317317</v>
       </c>
       <c r="N4" t="n">
-        <v>15.60912880495786</v>
+        <v>15.57066606174332</v>
       </c>
       <c r="O4" t="n">
-        <v>3.950839000131221</v>
+        <v>3.945968330048193</v>
       </c>
       <c r="P4" t="n">
-        <v>360.9862299276838</v>
+        <v>360.9797607434533</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -18081,28 +18127,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1288651145494793</v>
+        <v>0.1305742868805331</v>
       </c>
       <c r="J5" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K5" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0751239513922195</v>
+        <v>0.07723764312312964</v>
       </c>
       <c r="M5" t="n">
-        <v>2.744060327098376</v>
+        <v>2.744428330938518</v>
       </c>
       <c r="N5" t="n">
-        <v>11.70667854935197</v>
+        <v>11.70286852769453</v>
       </c>
       <c r="O5" t="n">
-        <v>3.421502381900672</v>
+        <v>3.420945560469287</v>
       </c>
       <c r="P5" t="n">
-        <v>367.1949507022223</v>
+        <v>367.1767575983341</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -18163,28 +18209,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05050007862373473</v>
+        <v>0.05334636424055879</v>
       </c>
       <c r="J6" t="n">
+        <v>372</v>
+      </c>
+      <c r="K6" t="n">
         <v>371</v>
       </c>
-      <c r="K6" t="n">
-        <v>370</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.006391469804014061</v>
+        <v>0.007146145268654647</v>
       </c>
       <c r="M6" t="n">
-        <v>3.631933495654563</v>
+        <v>3.635374481188635</v>
       </c>
       <c r="N6" t="n">
-        <v>22.49876974892302</v>
+        <v>22.51382993869344</v>
       </c>
       <c r="O6" t="n">
-        <v>4.743286808629962</v>
+        <v>4.744874069845631</v>
       </c>
       <c r="P6" t="n">
-        <v>367.5977084977242</v>
+        <v>367.5672159588327</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -18245,28 +18291,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09036548803149649</v>
+        <v>-0.08595801067973949</v>
       </c>
       <c r="J7" t="n">
+        <v>372</v>
+      </c>
+      <c r="K7" t="n">
         <v>371</v>
       </c>
-      <c r="K7" t="n">
-        <v>370</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01581556566404718</v>
+        <v>0.01432892207113035</v>
       </c>
       <c r="M7" t="n">
-        <v>4.438358879922647</v>
+        <v>4.447770310794392</v>
       </c>
       <c r="N7" t="n">
-        <v>28.83746311430171</v>
+        <v>28.94126090362253</v>
       </c>
       <c r="O7" t="n">
-        <v>5.370052431243265</v>
+        <v>5.379708254508095</v>
       </c>
       <c r="P7" t="n">
-        <v>370.9509810111816</v>
+        <v>370.903763271062</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -18327,28 +18373,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1473890492585558</v>
+        <v>-0.143739716306906</v>
       </c>
       <c r="J8" t="n">
+        <v>372</v>
+      </c>
+      <c r="K8" t="n">
         <v>371</v>
       </c>
-      <c r="K8" t="n">
-        <v>370</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04305440587939435</v>
+        <v>0.04109546303031086</v>
       </c>
       <c r="M8" t="n">
-        <v>4.328517300259874</v>
+        <v>4.335892741391531</v>
       </c>
       <c r="N8" t="n">
-        <v>27.4006063995948</v>
+        <v>27.45119821161567</v>
       </c>
       <c r="O8" t="n">
-        <v>5.234558854344347</v>
+        <v>5.239389106719949</v>
       </c>
       <c r="P8" t="n">
-        <v>366.3054639484853</v>
+        <v>366.2663682841928</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -18409,28 +18455,28 @@
         <v>0.1442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1194924129923515</v>
+        <v>-0.1172468715948054</v>
       </c>
       <c r="J9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03282032151823089</v>
+        <v>0.03176179317244887</v>
       </c>
       <c r="M9" t="n">
-        <v>3.930492227341552</v>
+        <v>3.930688704362221</v>
       </c>
       <c r="N9" t="n">
-        <v>24.09366399703944</v>
+        <v>24.07663971416361</v>
       </c>
       <c r="O9" t="n">
-        <v>4.908529718463507</v>
+        <v>4.906795259042669</v>
       </c>
       <c r="P9" t="n">
-        <v>370.5328027290107</v>
+        <v>370.5089003013922</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -18472,7 +18518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J372"/>
+  <dimension ref="A1:J373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37807,6 +37853,58 @@
         </is>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>-36.82715699999306,175.71491435172567</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>-36.82781108726634,175.7152957428689</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>-36.82845362488735,175.71569951979777</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>-36.82906609544919,175.71614824690914</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>-36.82965227785654,175.7166392970716</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>-36.830188703487956,175.71719251035262</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-36.83068188497064,175.71781853205363</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>-36.83106834375981,175.71857031431895</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0177/nzd0177.xlsx
+++ b/data/nzd0177/nzd0177.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J373"/>
+  <dimension ref="A1:J374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13866,6 +13866,42 @@
       <c r="J373" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="C374" t="n">
+        <v>363.31</v>
+      </c>
+      <c r="D374" t="n">
+        <v>366.39</v>
+      </c>
+      <c r="E374" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="F374" t="n">
+        <v>372.12</v>
+      </c>
+      <c r="G374" t="n">
+        <v>375.76</v>
+      </c>
+      <c r="H374" t="n">
+        <v>367.99</v>
+      </c>
+      <c r="I374" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B383"/>
+  <dimension ref="A1:B384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17713,6 +17749,16 @@
       </c>
       <c r="B383" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -17881,28 +17927,28 @@
         <v>0.1672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3140450236980741</v>
+        <v>0.3118410334972169</v>
       </c>
       <c r="J2" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K2" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1721480991192771</v>
+        <v>0.1707740265634636</v>
       </c>
       <c r="M2" t="n">
-        <v>4.135909311755986</v>
+        <v>4.132944061787657</v>
       </c>
       <c r="N2" t="n">
-        <v>27.24898909079061</v>
+        <v>27.22172729456282</v>
       </c>
       <c r="O2" t="n">
-        <v>5.220056426015969</v>
+        <v>5.217444517631483</v>
       </c>
       <c r="P2" t="n">
-        <v>363.2867231718207</v>
+        <v>363.3102901475874</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17963,28 +18009,28 @@
         <v>0.1707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2605866675876077</v>
+        <v>0.2592555938636242</v>
       </c>
       <c r="J3" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K3" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1946148018563556</v>
+        <v>0.1938038544702839</v>
       </c>
       <c r="M3" t="n">
-        <v>3.114795169649379</v>
+        <v>3.11233012542476</v>
       </c>
       <c r="N3" t="n">
-        <v>16.14538120788583</v>
+        <v>16.11879816046534</v>
       </c>
       <c r="O3" t="n">
-        <v>4.018131556816654</v>
+        <v>4.014822307458369</v>
       </c>
       <c r="P3" t="n">
-        <v>358.7375625279483</v>
+        <v>358.7517955232604</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -18045,28 +18091,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2239228301669287</v>
+        <v>0.2235642319655867</v>
       </c>
       <c r="J4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L4" t="n">
-        <v>0.156128449972663</v>
+        <v>0.1564994735016904</v>
       </c>
       <c r="M4" t="n">
-        <v>3.042742613317317</v>
+        <v>3.036441940591649</v>
       </c>
       <c r="N4" t="n">
-        <v>15.57066606174332</v>
+        <v>15.53013387738149</v>
       </c>
       <c r="O4" t="n">
-        <v>3.945968330048193</v>
+        <v>3.940829085025318</v>
       </c>
       <c r="P4" t="n">
-        <v>360.9797607434533</v>
+        <v>360.9835951865999</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -18127,28 +18173,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1305742868805331</v>
+        <v>0.1319440944611564</v>
       </c>
       <c r="J5" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K5" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07723764312312964</v>
+        <v>0.0790714683067949</v>
       </c>
       <c r="M5" t="n">
-        <v>2.744428330938518</v>
+        <v>2.743243483368628</v>
       </c>
       <c r="N5" t="n">
-        <v>11.70286852769453</v>
+        <v>11.68918190098192</v>
       </c>
       <c r="O5" t="n">
-        <v>3.420945560469287</v>
+        <v>3.418944559506913</v>
       </c>
       <c r="P5" t="n">
-        <v>367.1767575983341</v>
+        <v>367.162110427015</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -18209,28 +18255,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05334636424055879</v>
+        <v>0.05500587778794713</v>
       </c>
       <c r="J6" t="n">
+        <v>373</v>
+      </c>
+      <c r="K6" t="n">
         <v>372</v>
       </c>
-      <c r="K6" t="n">
-        <v>371</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.007146145268654647</v>
+        <v>0.007631880812040359</v>
       </c>
       <c r="M6" t="n">
-        <v>3.635374481188635</v>
+        <v>3.633228529892081</v>
       </c>
       <c r="N6" t="n">
-        <v>22.51382993869344</v>
+        <v>22.47893079519261</v>
       </c>
       <c r="O6" t="n">
-        <v>4.744874069845631</v>
+        <v>4.741195080904456</v>
       </c>
       <c r="P6" t="n">
-        <v>367.5672159588327</v>
+        <v>367.5493571049012</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -18291,28 +18337,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08595801067973949</v>
+        <v>-0.0821091879801036</v>
       </c>
       <c r="J7" t="n">
+        <v>373</v>
+      </c>
+      <c r="K7" t="n">
         <v>372</v>
       </c>
-      <c r="K7" t="n">
-        <v>371</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01432892207113035</v>
+        <v>0.01310846988975001</v>
       </c>
       <c r="M7" t="n">
-        <v>4.447770310794392</v>
+        <v>4.454518291722745</v>
       </c>
       <c r="N7" t="n">
-        <v>28.94126090362253</v>
+        <v>29.00127971205218</v>
       </c>
       <c r="O7" t="n">
-        <v>5.379708254508095</v>
+        <v>5.385283624104879</v>
       </c>
       <c r="P7" t="n">
-        <v>370.903763271062</v>
+        <v>370.8623441681513</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -18373,28 +18419,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.143739716306906</v>
+        <v>-0.1407301879602281</v>
       </c>
       <c r="J8" t="n">
+        <v>373</v>
+      </c>
+      <c r="K8" t="n">
         <v>372</v>
       </c>
-      <c r="K8" t="n">
-        <v>371</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04109546303031086</v>
+        <v>0.03957555643042177</v>
       </c>
       <c r="M8" t="n">
-        <v>4.335892741391531</v>
+        <v>4.340000979390104</v>
       </c>
       <c r="N8" t="n">
-        <v>27.45119821161567</v>
+        <v>27.46166956308991</v>
       </c>
       <c r="O8" t="n">
-        <v>5.239389106719949</v>
+        <v>5.240388302701424</v>
       </c>
       <c r="P8" t="n">
-        <v>366.2663682841928</v>
+        <v>366.2339812469007</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -18455,28 +18501,28 @@
         <v>0.1442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1172468715948054</v>
+        <v>-0.1160413662881233</v>
       </c>
       <c r="J9" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K9" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03176179317244887</v>
+        <v>0.03129937302665242</v>
       </c>
       <c r="M9" t="n">
-        <v>3.930688704362221</v>
+        <v>3.925958172535891</v>
       </c>
       <c r="N9" t="n">
-        <v>24.07663971416361</v>
+        <v>24.02579064135132</v>
       </c>
       <c r="O9" t="n">
-        <v>4.906795259042669</v>
+        <v>4.901611025096884</v>
       </c>
       <c r="P9" t="n">
-        <v>370.5089003013922</v>
+        <v>370.4960099925613</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -18518,7 +18564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J373"/>
+  <dimension ref="A1:J374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37905,6 +37951,58 @@
         </is>
       </c>
     </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>-36.82716646553828,175.71489294860206</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>-36.827822059801996,175.7152694969626</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>-36.828460836306085,175.7156817046766</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>-36.82906887657885,175.71614248180765</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>-36.829663973237345,175.71661981266146</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>-36.83019506148315,175.71718473093634</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>-36.83069030047319,175.71781101685764</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>-36.83108293355946,175.7185583472228</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
